--- a/artfynd/A 30478-2025 artfynd.xlsx
+++ b/artfynd/A 30478-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212076</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212077</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212081</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212080</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212084</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212047</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,8 +1410,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212087</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30478-2025 artfynd.xlsx
+++ b/artfynd/A 30478-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,64 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110212076</v>
+        <v>136151704</v>
       </c>
       <c r="B2" t="n">
-        <v>80432</v>
+        <v>100564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2082</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söder om Näsåker, nära älven., Ång</t>
+          <t>Bäckravin, Bastuvallen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594983</v>
+        <v>594740</v>
       </c>
       <c r="R2" t="n">
-        <v>7035170</v>
+        <v>7035362</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +761,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>3 sub.</t>
+          <t>Ca 10 tuvor. Kan finnas fler längre västerut i ravinen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,60 +780,56 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>På samtliga stammar av trestammig sälg.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Klara Elmquist, Johanna Kühne</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110212076</t>
+          <t>https://artportalen.se/Sighting/136151704</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110212077</v>
+        <v>110212076</v>
       </c>
       <c r="B3" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594976</v>
+        <v>594983</v>
       </c>
       <c r="R3" t="n">
-        <v>7035161</v>
+        <v>7035170</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,6 +877,11 @@
           <t>2022-06-15</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3 sub.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -876,7 +893,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Sälglåga</t>
+          <t>På samtliga stammar av trestammig sälg.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -893,55 +910,51 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110212077</t>
+          <t>https://artportalen.se/Sighting/110212076</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110212081</v>
+        <v>110212077</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Söder om Näsåker, nära älven., Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594932</v>
+        <v>594976</v>
       </c>
       <c r="R4" t="n">
-        <v>7035212</v>
+        <v>7035161</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,11 +989,6 @@
           <t>2022-06-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>I blockig, mossig granskog i nordbrant.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -989,6 +997,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sälglåga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1004,51 +1017,55 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110212081</t>
+          <t>https://artportalen.se/Sighting/110212077</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110212080</v>
+        <v>110212081</v>
       </c>
       <c r="B5" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Söder om Näsåker, nära älven., Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594957</v>
+        <v>594932</v>
       </c>
       <c r="R5" t="n">
-        <v>7035196</v>
+        <v>7035212</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,6 +1100,11 @@
           <t>2022-06-15</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I blockig, mossig granskog i nordbrant.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1106,13 +1128,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110212080</t>
+          <t>https://artportalen.se/Sighting/110212081</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110212084</v>
+        <v>110212080</v>
       </c>
       <c r="B6" t="n">
         <v>97983</v>
@@ -1147,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594864</v>
+        <v>594957</v>
       </c>
       <c r="R6" t="n">
-        <v>7035261</v>
+        <v>7035196</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,16 +1230,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110212084</t>
+          <t>https://artportalen.se/Sighting/110212080</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110212047</v>
+        <v>110212084</v>
       </c>
       <c r="B7" t="n">
-        <v>101228</v>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,16 +1247,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1249,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594825</v>
+        <v>594864</v>
       </c>
       <c r="R7" t="n">
-        <v>7035336</v>
+        <v>7035261</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1310,13 +1332,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110212047</t>
+          <t>https://artportalen.se/Sighting/110212084</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110212087</v>
+        <v>110212047</v>
       </c>
       <c r="B8" t="n">
         <v>101228</v>
@@ -1351,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594855</v>
+        <v>594825</v>
       </c>
       <c r="R8" t="n">
-        <v>7035271</v>
+        <v>7035336</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1411,6 +1433,108 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212047</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>110212087</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Söder om Näsåker, nära älven., Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>594855</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7035271</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-06-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-06-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110212087</t>
         </is>
@@ -1425,6 +1549,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30478-2025 artfynd.xlsx
+++ b/artfynd/A 30478-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136151704</v>
       </c>
       <c r="B2" t="n">
-        <v>100564</v>
+        <v>100565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30478-2025 artfynd.xlsx
+++ b/artfynd/A 30478-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136151704</v>
       </c>
       <c r="B2" t="n">
-        <v>100565</v>
+        <v>100566</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30478-2025 artfynd.xlsx
+++ b/artfynd/A 30478-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136151704</v>
       </c>
       <c r="B2" t="n">
-        <v>100566</v>
+        <v>100572</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30478-2025 artfynd.xlsx
+++ b/artfynd/A 30478-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136151704</v>
       </c>
       <c r="B2" t="n">
-        <v>100572</v>
+        <v>100573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30478-2025 artfynd.xlsx
+++ b/artfynd/A 30478-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136151704</v>
       </c>
       <c r="B2" t="n">
-        <v>100573</v>
+        <v>100584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30478-2025 artfynd.xlsx
+++ b/artfynd/A 30478-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136151704</v>
       </c>
       <c r="B2" t="n">
-        <v>100584</v>
+        <v>100597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30478-2025 artfynd.xlsx
+++ b/artfynd/A 30478-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136151704</v>
       </c>
       <c r="B2" t="n">
-        <v>100597</v>
+        <v>100598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30478-2025 artfynd.xlsx
+++ b/artfynd/A 30478-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136151704</v>
       </c>
       <c r="B2" t="n">
-        <v>100598</v>
+        <v>100611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30478-2025 artfynd.xlsx
+++ b/artfynd/A 30478-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136151704</v>
       </c>
       <c r="B2" t="n">
-        <v>100611</v>
+        <v>100612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
